--- a/data/analysis_results/gpt-4.1_vs_gpt-4.1-error/Llama-3.3-70B-Instruct/metrics_default_vs_basic.xlsx
+++ b/data/analysis_results/gpt-4.1_vs_gpt-4.1-error/Llama-3.3-70B-Instruct/metrics_default_vs_basic.xlsx
@@ -420,16 +420,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.09322033898305085</v>
+        <v>0.1016949152542373</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2183098591549296</v>
+        <v>0.2253521126760563</v>
       </c>
       <c r="D2">
-        <v>0.9098360655737705</v>
+        <v>0.9016393442622951</v>
       </c>
       <c r="E2">
         <v>118</v>

--- a/data/analysis_results/gpt-4.1_vs_gpt-4.1-error/Llama-3.3-70B-Instruct/metrics_default_vs_basic.xlsx
+++ b/data/analysis_results/gpt-4.1_vs_gpt-4.1-error/Llama-3.3-70B-Instruct/metrics_default_vs_basic.xlsx
@@ -420,16 +420,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.1016949152542373</v>
+        <v>0.09322033898305085</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2253521126760563</v>
+        <v>0.2183098591549296</v>
       </c>
       <c r="D2">
-        <v>0.9016393442622951</v>
+        <v>0.9098360655737705</v>
       </c>
       <c r="E2">
         <v>118</v>
